--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/validation/D2_scientific_validation_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/validation/D2_scientific_validation_source_data.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analyte_effects" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D1_D2_concordance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_pairs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTI_component_audit" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTI_threshold_reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -547,7 +549,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9868131868131869</v>
+        <v>0.9866666666666665</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -556,13 +558,13 @@
         <v>1999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9898270600203459</v>
+        <v>0.9674556213017751</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9815370370370371</v>
+        <v>0.9545892039845644</v>
       </c>
       <c r="J2" t="n">
-        <v>0.995467623108149</v>
+        <v>0.9789277071990321</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -583,10 +585,10 @@
         <v>61</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01147104814806171</v>
+        <v>0.01183280042943497</v>
       </c>
       <c r="R2" t="n">
-        <v>4.951448176371205</v>
+        <v>4.951173058061568</v>
       </c>
     </row>
     <row r="3">
@@ -607,7 +609,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9956043956043955</v>
+        <v>0.9868131868131869</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -616,13 +618,13 @@
         <v>2000</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9959225280326198</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.9907271768473962</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.9991424950172477</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -643,10 +645,10 @@
         <v>61</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01140103157747334</v>
       </c>
       <c r="R3" t="n">
-        <v>4.953867739837271</v>
+        <v>4.953331441022224</v>
       </c>
     </row>
     <row r="4">
@@ -667,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9780219780219781</v>
+        <v>0.9824175824175824</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -676,37 +678,37 @@
         <v>2000</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9188078108941419</v>
+        <v>0.9775739041794088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8799939117199391</v>
+        <v>0.9647887323943662</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9458155909938493</v>
+        <v>0.9866678743961352</v>
       </c>
       <c r="K4" t="n">
-        <v>0.819672131147541</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7213114754098361</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9032258064516129</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>61</v>
       </c>
       <c r="O4" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01043246901766751</v>
+        <v>0.01119098186570822</v>
       </c>
       <c r="R4" t="n">
-        <v>4.955898069193856</v>
+        <v>4.955182444655771</v>
       </c>
     </row>
     <row r="5">
@@ -727,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9910989010989011</v>
+        <v>0.9868131868131869</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -736,13 +738,13 @@
         <v>2000</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9788732394366197</v>
+        <v>0.98001998001998</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9678944891570553</v>
+        <v>0.9716466739367503</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9872778475114073</v>
+        <v>0.9871028423252951</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -763,10 +765,10 @@
         <v>61</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01159941186080706</v>
+        <v>0.01168109785982683</v>
       </c>
       <c r="R5" t="n">
-        <v>4.951254327326112</v>
+        <v>4.951144478450073</v>
       </c>
     </row>
     <row r="6">
@@ -823,10 +825,10 @@
         <v>61</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01144770929119892</v>
       </c>
       <c r="R6" t="n">
-        <v>4.953959310204074</v>
+        <v>4.953484111758422</v>
       </c>
     </row>
     <row r="7">
@@ -847,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9824175824175824</v>
+        <v>0.9823543388724547</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -856,13 +858,13 @@
         <v>2000</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9568345323741008</v>
+        <v>0.9918450560652395</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9424726302344677</v>
+        <v>0.9851729437074112</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9682542753943683</v>
+        <v>0.9968288363609573</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -883,10 +885,10 @@
         <v>61</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01086423786962915</v>
+        <v>0.01135435386374775</v>
       </c>
       <c r="R7" t="n">
-        <v>4.956078026540623</v>
+        <v>4.955420695616054</v>
       </c>
     </row>
     <row r="8">
@@ -916,13 +918,13 @@
         <v>2000</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9567354965585054</v>
+        <v>0.938755980861244</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9474183877415057</v>
+        <v>0.9223092081435025</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9639563163687503</v>
+        <v>0.9504883176602179</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -943,10 +945,10 @@
         <v>61</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01186780871472915</v>
+        <v>0.01219455271080822</v>
       </c>
       <c r="R8" t="n">
-        <v>4.950963553758474</v>
+        <v>4.951089939604397</v>
       </c>
     </row>
     <row r="9">
@@ -967,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9864864864864863</v>
+        <v>0.9866666666666665</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -976,13 +978,13 @@
         <v>2000</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9918450560652395</v>
+        <v>0.981</v>
       </c>
       <c r="I9" t="n">
-        <v>0.984764635806105</v>
+        <v>0.972866842597174</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9968279771921512</v>
+        <v>0.9883236700501029</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -1003,10 +1005,10 @@
         <v>61</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01144770929119892</v>
+        <v>0.01166942843139543</v>
       </c>
       <c r="R9" t="n">
-        <v>4.9539081373859</v>
+        <v>4.953561738794368</v>
       </c>
     </row>
     <row r="10">
@@ -1036,10 +1038,10 @@
         <v>2000</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.9979612640163099</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.9944317994738036</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1063,10 +1065,10 @@
         <v>61</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01142437043433613</v>
       </c>
       <c r="R10" t="n">
-        <v>4.956275515102371</v>
+        <v>4.955764824516132</v>
       </c>
     </row>
   </sheetData>
@@ -1130,13 +1132,13 @@
         <v>0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>4.953665704981972</v>
+        <v>4.9531395964249</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01140103157747334</v>
+        <v>0.01151772586178729</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3447496087722789</v>
+        <v>0.3469098947526273</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -1151,13 +1153,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>4.953959310204074</v>
+        <v>4.95348411175842</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01144770929119892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3437634840160546</v>
+        <v>0.3457260315316389</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -1172,13 +1174,13 @@
         <v>1.2</v>
       </c>
       <c r="C4" t="n">
-        <v>4.954146949467357</v>
+        <v>4.953738650562348</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01143603986276752</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3431346029670677</v>
+        <v>0.3446885262561912</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -1193,13 +1195,13 @@
         <v>0.8</v>
       </c>
       <c r="C5" t="n">
-        <v>4.95290209067363</v>
+        <v>4.952375442361952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01138936214904194</v>
+        <v>0.01159941186080706</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3455989640025759</v>
+        <v>0.3480998021181996</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -1214,13 +1216,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>4.953959310204074</v>
+        <v>4.95348411175842</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01144770929119892</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3437634840160546</v>
+        <v>0.3457260315316389</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -1235,13 +1237,13 @@
         <v>1.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4.954519095462722</v>
+        <v>4.954055476668795</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01135435386374775</v>
+        <v>0.01138936214904194</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3423040553188827</v>
+        <v>0.3441157638182727</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -1512,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="3">
@@ -1623,7 +1625,7 @@
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="6">
@@ -1660,7 +1662,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="7">
@@ -1771,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="10">
@@ -1808,7 +1810,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="11">
@@ -1919,7 +1921,7 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="14">
@@ -1956,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="15">
@@ -2067,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="18">
@@ -2104,7 +2106,7 @@
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="19">
@@ -2252,7 +2254,7 @@
         <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="23">
@@ -2400,7 +2402,7 @@
         <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="27">
@@ -2548,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="31">
@@ -2696,7 +2698,7 @@
         <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006029049054535489</v>
       </c>
     </row>
     <row r="35">
@@ -2807,7 +2809,7 @@
         <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="38">
@@ -2844,7 +2846,7 @@
         <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="39">
@@ -2955,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="42">
@@ -2992,7 +2994,7 @@
         <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="43">
@@ -3103,7 +3105,7 @@
         <v>5</v>
       </c>
       <c r="I45" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="46">
@@ -3140,7 +3142,7 @@
         <v>5</v>
       </c>
       <c r="I46" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="47">
@@ -3288,7 +3290,7 @@
         <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="51">
@@ -3399,7 +3401,7 @@
         <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>0.007673335160317895</v>
+        <v>0.007947382844614962</v>
       </c>
     </row>
     <row r="54">
@@ -3436,7 +3438,7 @@
         <v>5</v>
       </c>
       <c r="I54" t="n">
-        <v>0.005480953685941353</v>
+        <v>0.006303096738832557</v>
       </c>
     </row>
     <row r="55">
@@ -3584,7 +3586,7 @@
         <v>5</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="59">
@@ -3732,7 +3734,7 @@
         <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="63">
@@ -3880,7 +3882,7 @@
         <v>5</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="67">
@@ -4028,7 +4030,7 @@
         <v>5</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="71">
@@ -4176,7 +4178,7 @@
         <v>5</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -4324,7 +4326,7 @@
         <v>5</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="79">
@@ -4472,7 +4474,7 @@
         <v>5</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -4620,7 +4622,7 @@
         <v>5</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="87">
@@ -4768,7 +4770,7 @@
         <v>5</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="91">
@@ -4916,7 +4918,7 @@
         <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="95">
@@ -5064,7 +5066,7 @@
         <v>5</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="99">
@@ -5212,7 +5214,7 @@
         <v>5</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="103">
@@ -5360,7 +5362,7 @@
         <v>5</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="107">
@@ -5508,7 +5510,7 @@
         <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="111">
@@ -5656,7 +5658,7 @@
         <v>5</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="115">
@@ -5804,7 +5806,7 @@
         <v>5</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="119">
@@ -5952,7 +5954,7 @@
         <v>5</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="123">
@@ -6100,7 +6102,7 @@
         <v>5</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="127">
@@ -6248,7 +6250,7 @@
         <v>5</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="131">
@@ -6396,7 +6398,7 @@
         <v>5</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="135">
@@ -6544,7 +6546,7 @@
         <v>5</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="139">
@@ -6692,7 +6694,7 @@
         <v>5</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="143">
@@ -6840,7 +6842,7 @@
         <v>5</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="147">
@@ -6988,7 +6990,7 @@
         <v>5</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="151">
@@ -7136,7 +7138,7 @@
         <v>5</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="155">
@@ -7284,7 +7286,7 @@
         <v>5</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="159">
@@ -7432,7 +7434,7 @@
         <v>5</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="163">
@@ -7580,7 +7582,7 @@
         <v>5</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>0.002450980392156863</v>
       </c>
     </row>
     <row r="167">
@@ -7752,19 +7754,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.661859759278684e-05</v>
+        <v>1.687138321582182e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.42912665893158e-06</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="D2" t="n">
-        <v>8.28080804913256e-05</v>
+        <v>4.178508664680614e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000843986142688604</v>
+        <v>0.0004245863535839713</v>
       </c>
       <c r="F2" t="n">
-        <v>3.615019966499672e-05</v>
+        <v>3.621352965998559e-05</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7779,19 +7781,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001505558580383592</v>
+        <v>0.000166557015443658</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.485729205441544e-06</v>
+        <v>1.525829280257796e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003655349572451172</v>
+        <v>0.0003739709530909731</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003209372325459556</v>
+        <v>0.003693660548651408</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000160875434946678</v>
+        <v>0.0001694021566388865</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7806,19 +7808,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008772602118228612</v>
+        <v>0.00818732241066833</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0001907990680035443</v>
+        <v>-0.0001888947828914356</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02441012366674527</v>
+        <v>0.02264912639501868</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2575121659008299</v>
+        <v>0.2504654889425305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008772602118228166</v>
+        <v>0.008187322410669795</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7833,19 +7835,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005441339164492298</v>
+        <v>0.005439182897578831</v>
       </c>
       <c r="C5" t="n">
-        <v>-4.383297910119932e-05</v>
+        <v>-4.278342772394694e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01394899820787616</v>
+        <v>0.01394681759998886</v>
       </c>
       <c r="E5" t="n">
-        <v>0.106829384520722</v>
+        <v>0.106327570340959</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005442520617437501</v>
+        <v>0.005440140601655514</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -8154,4 +8156,4964 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sensor_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q_TI_mean</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>observed_weight_mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>missing_deficit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>irregular_deficit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>duplicate_deficit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>out_of_order_deficit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.966515169392559</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.03348483060744129</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4.966526476852608</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03347352314739179</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.966377267542825</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03362273245717536</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.966525493595213</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0334745064047874</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.966607841402094</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0333921585979052</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4.966612511874724</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.03338748812527607</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.966620869562586</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0333791304374134</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4.966632668651334</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0333673313486661</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.966574164836295</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03342583516370479</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4.96652623103826</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.03347376896174069</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.966523772894771</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.03347622710522972</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4.966605874887303</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.03339412511269643</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4.966580064380668</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03341993561933114</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.966611036988631</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.03338896301136948</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sensor_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>development_start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>development_end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>candidate_high_quality_rule</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>support_n</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>unique_value_n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>q75</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>q90</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>q95</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>q99</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>production_b0</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>production_b1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>production_b2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>production_b3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>production_b4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>degenerate_reference</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.002777777777777778</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3495</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>3495</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>3495</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3495</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R45" t="b">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H50" t="n">
+        <v>9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>missing_rate</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H54" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>independent_SAP_lock_required_before_production_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>true_irregular_rate</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R55" t="b">
+        <v>1</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>duplicate_rate</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>out_of_order_rate</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-12-31 23:59:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Q_GS&gt;=4.5 and Q_FA&gt;=4.5</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>sensitivity_only_not_adopted</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>zero_or_sparse_empirical_support_requires_engineering_floor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/validation/D2_scientific_validation_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/validation/D2_scientific_validation_source_data.xlsx
@@ -24,7 +24,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_vs_score_impact" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="low_tail_events" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="veto_reasons" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sensitive_diagnostics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel_outcome" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel_veto" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sensitive_diagnostics" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25791,15 +25793,914 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>sensor_id</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_sensor_hours</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_D2_Strict</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p05_D2_Strict</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>q25_D2_Strict</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>median_D2_Strict</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>q75_D2_Strict</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p95_D2_Strict</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>low_hours_per_1000h</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>veto_hours_per_1000h</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>grade_A_pct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>grade_B_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>grade_C_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>grade_D_pct</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>grade_E_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.95969311097208</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M2" t="n">
+        <v>98.02319882372161</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9965691880411697</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.959678129827932</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M3" t="n">
+        <v>98.02319882372161</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9965691880411697</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.959584550737319</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M4" t="n">
+        <v>98.03953602352557</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9802319882372161</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.959549489076767</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M5" t="n">
+        <v>98.03953602352557</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9802319882372161</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.959297978162197</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M6" t="n">
+        <v>98.03953602352557</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9802319882372161</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.958891111258255</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M7" t="n">
+        <v>98.02319882372161</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9965691880411697</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.958802624313989</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M8" t="n">
+        <v>97.94151282470185</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.078255187060938</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.958750182170779</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M9" t="n">
+        <v>97.94151282470185</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.078255187060938</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.958655165394208</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M10" t="n">
+        <v>97.94151282470185</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.078255187060938</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.958468053604856</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.312203888253554</v>
+      </c>
+      <c r="M11" t="n">
+        <v>97.94151282470185</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.078255187060938</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04901159941186081</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.950962435055505</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12.41627185100474</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.41627185100474</v>
+      </c>
+      <c r="M12" t="n">
+        <v>97.64744322823069</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.045580787453031</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3757555954909328</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.950919242267472</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12.41627185100474</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.41627185100474</v>
+      </c>
+      <c r="M13" t="n">
+        <v>97.64744322823069</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.045580787453031</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.3757555954909328</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.950880157238672</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12.41627185100474</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12.41627185100474</v>
+      </c>
+      <c r="M14" t="n">
+        <v>97.64744322823069</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.045580787453031</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3757555954909328</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6121</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.940616378333655</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12.57964384904427</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12.57964384904427</v>
+      </c>
+      <c r="M15" t="n">
+        <v>96.61819964058161</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.009475575886293</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4411043947067473</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9312203888253554</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sensor_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>analyte</t>
@@ -25807,273 +26708,260 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>soft_stasis_fraction</t>
+          <t>reason_group</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>intrinsic_soft_hour_rate</t>
+          <t>veto_hours</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>peer_response_loss_hour_rate</t>
+          <t>veto_share_pct</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>joint_soft_hour_rate</t>
+          <t>veto_hours_per_1000h</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>sustained_quasi_freeze_hour_rate</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>production_Q_HA_low_rate</t>
+          <t>display_order</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DO_1_1</t>
+          <t>ORP_2_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.002295376572455481</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008495343898055873</v>
+        <v>43.85964912280701</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.084299950988401</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DO_1_2</t>
+          <t>ORP_2_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0007787398573217884</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0040842999509884</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.490115994118608</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>ORP_2_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0009257746555573707</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01306975984316288</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4.737787943146545</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DO_1_4</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5849479932472906</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7026629635680445</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>43.85964912280701</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.084299950988401</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DO_2_1</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.02782724318829531</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01437673582747917</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01176278385884659</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002613951968632576</v>
+        <v>0.490115994118608</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001960463976474432</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.00571801993138376</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DO_2_2</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.006793552251810706</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0.003104067962751185</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03528835157653978</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001960463976474432</v>
+        <v>4.737787943146545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001470347982355824</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.003594183956869793</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.003076839296411261</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>0.003104067962751185</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000163371998039536</v>
+        <v>43.85964912280701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000163371998039536</v>
+        <v>4.084299950988401</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.003594183956869793</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DO_2_4</t>
+          <t>ORP_1_1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1935967252990615</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1385394543375265</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.490115994118608</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.003594183956869793</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -26087,23 +26975,22 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>0.1203293761004919</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.002123835974513968</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01911452377062571</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="F10" t="n">
-        <v>0.000490115994118608</v>
+        <v>4.737787943146545</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -26117,29 +27004,28 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>0.116784203743034</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01143603986276752</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009148831890214017</v>
+        <v>43.85964912280701</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00163371998039536</v>
+        <v>4.084299950988401</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000326743996079072</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORP_1_3</t>
+          <t>ORP_1_2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -26147,29 +27033,28 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0.09343607616765598</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.07319065512171213</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01012906387845123</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009148831890214017</v>
+        <v>0.490115994118608</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005391275935304689</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORP_2_1</t>
+          <t>ORP_1_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -26177,29 +27062,28 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0.2089064967597887</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04378369547459565</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02908021565103741</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009148831890214017</v>
+        <v>4.737787943146545</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00163371998039536</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORP_2_2</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -26207,53 +27091,979 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0.379582584545009</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2707074007515112</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1079888907041333</v>
+        <v>43.85964912280701</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08201274301584709</v>
+        <v>4.084299950988401</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04247671949027937</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50.87719298245614</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>ORP_2_3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ORP</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0.3069455789722086</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3051788923378533</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1414801503022382</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.1351086423786963</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.1003104067962751</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>43.85964912280701</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>29</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50.87719298245614</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>43.85964912280701</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>29</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50.87719298245614</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>43.85964912280701</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>29</v>
+      </c>
+      <c r="E25" t="n">
+        <v>50.87719298245614</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>43.85964912280701</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50.87719298245614</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" t="n">
+        <v>43.85964912280701</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" t="n">
+        <v>50.87719298245614</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>32.89473684210527</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.947368421052631</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hard stasis</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>19</v>
+      </c>
+      <c r="E34" t="n">
+        <v>25</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.104067962751185</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>29</v>
+      </c>
+      <c r="E35" t="n">
+        <v>38.15789473684211</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32.89473684210527</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.947368421052631</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G37" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hard stasis</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.104067962751185</v>
+      </c>
+      <c r="G38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>29</v>
+      </c>
+      <c r="E39" t="n">
+        <v>38.15789473684211</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>25</v>
+      </c>
+      <c r="E40" t="n">
+        <v>32.89473684210527</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.947368421052631</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G41" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Hard stasis</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>19</v>
+      </c>
+      <c r="E42" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.104067962751185</v>
+      </c>
+      <c r="G42" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>29</v>
+      </c>
+      <c r="E43" t="n">
+        <v>38.15789473684211</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gap + missing</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>25</v>
+      </c>
+      <c r="E44" t="n">
+        <v>32.46753246753246</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.084299950988401</v>
+      </c>
+      <c r="G44" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Gap only</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.896103896103896</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.490115994118608</v>
+      </c>
+      <c r="G45" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Hard stasis</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" t="n">
+        <v>25.97402597402597</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.26743996079072</v>
+      </c>
+      <c r="G46" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Missing only</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>37.66233766233766</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.737787943146545</v>
+      </c>
+      <c r="G47" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -26609,6 +28419,482 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sensor_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>soft_stasis_fraction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>intrinsic_soft_hour_rate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>peer_response_loss_hour_rate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>joint_soft_hour_rate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sustained_quasi_freeze_hour_rate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>production_Q_HA_low_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.002295376572455481</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.008495343898055873</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0007787398573217884</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0040842999509884</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0009257746555573707</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01306975984316288</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5849479932472906</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7026629635680445</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02782724318829531</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01437673582747917</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01176278385884659</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.002613951968632576</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001960463976474432</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.00571801993138376</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.006793552251810706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.003104067962751185</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.03528835157653978</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.001960463976474432</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001470347982355824</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.003594183956869793</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.003076839296411261</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.003104067962751185</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.000163371998039536</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.000163371998039536</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.003594183956869793</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1935967252990615</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1385394543375265</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.003594183956869793</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1203293761004919</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.002123835974513968</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01911452377062571</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.000490115994118608</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.116784203743034</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01143603986276752</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.009148831890214017</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00163371998039536</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.000326743996079072</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.09343607616765598</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.07319065512171213</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01012906387845123</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.009148831890214017</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005391275935304689</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2089064967597887</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04378369547459565</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02908021565103741</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.009148831890214017</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.00163371998039536</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.379582584545009</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2707074007515112</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1079888907041333</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.08201274301584709</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.04247671949027937</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3069455789722086</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3051788923378533</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1414801503022382</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1351086423786963</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1003104067962751</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
